--- a/teste_script/documentacao_leblon/RAG Manutenção.xlsx
+++ b/teste_script/documentacao_leblon/RAG Manutenção.xlsx
@@ -58,7 +58,7 @@
     <t>INDMANTMANUAL</t>
   </si>
   <si>
-    <t>TABELA INDICADORES MANUAIS. Auxilia o cálculo de alguns indicadores manuais.</t>
+    <t xml:space="preserve">TABELA INDICADORES MANUAIS. USAR APENAS PARA PERGUNTAS COM OS SEGUINTES INDICADORES: CAIEFO, CDTDM, QVA, QVV, TIC, TO, TOPP, </t>
   </si>
   <si>
     <t>Nome da Planilha</t>
@@ -1015,7 +1015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="30.75" customHeight="1">
+    <row r="7" ht="58.5" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
